--- a/doc/関数一覧表.xlsx
+++ b/doc/関数一覧表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://b0aa600df9934664bf4b-my.sharepoint.com/personal/masaharu_itou_ab_east_ntt_co_jp/Documents/ドキュメント/GitHub/SOSDB_Analyzer/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://b0aa600df9934664bf4b-my.sharepoint.com/personal/masaharu_itou_ab_east_ntt_co_jp/Documents/ドキュメント/GitHub/SOSDB_Analyzer/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="4748" documentId="11_F25DC773A252ABDACC104879F99B4D3C5ADE58FC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC7D6620-33DF-4B52-A274-F4CA85FF9986}"/>
   <bookViews>
-    <workbookView xWindow="2820" yWindow="465" windowWidth="17850" windowHeight="14430" xr2:uid="{88006736-0FAD-489A-A5AE-E098658DFC08}"/>
+    <workbookView xWindow="1095" yWindow="2265" windowWidth="25980" windowHeight="12870" xr2:uid="{88006736-0FAD-489A-A5AE-E098658DFC08}"/>
   </bookViews>
   <sheets>
     <sheet name="関数依存関係" sheetId="40" r:id="rId1"/>
